--- a/AAII_Financials/Quarterly/SNMCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNMCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="92">
   <si>
     <t>SNMCY</t>
   </si>
@@ -656,83 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,8 +786,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +839,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +892,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +917,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +966,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1019,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1072,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1125,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,8 +1147,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1142,8 +1196,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,8 +1249,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,8 +1274,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1255,8 +1323,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,8 +1376,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,8 +1429,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1396,8 +1482,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1443,8 +1535,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,8 +1588,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1537,8 +1641,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1584,8 +1694,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1747,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1800,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,8 +1906,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1819,8 +1959,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1866,8 +2012,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,8 +2065,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1960,60 +2118,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,102 +2222,116 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>689700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>684200</v>
+      </c>
+      <c r="F41" s="3">
         <v>662400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>656800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>892300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>848800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>653500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>732200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>489700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>478600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2554200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2417900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3791000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3819500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4943200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4685600</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>67900</v>
+      </c>
+      <c r="F42" s="3">
         <v>99400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>98600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>77400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>73600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>48700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>47600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2284300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2162400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1833600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1847400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1325400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1256300</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2155,44 +2341,50 @@
       <c r="E43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>4600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>124800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>121900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>124700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>118100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>135800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>136800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2134200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2022900</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2238,243 +2430,279 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>834300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>827700</v>
+      </c>
+      <c r="F45" s="3">
         <v>1015900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1007300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>841100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>800200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1253200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1404000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>57595400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>56292100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1508500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1428000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1373700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1384000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2518200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2386900</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1592500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1579900</v>
+      </c>
+      <c r="F46" s="3">
         <v>1777600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1762700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1815400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1727000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1906700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2136200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>58258600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>56940300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>6471700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6126300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7134100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>7187700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>10921000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10351800</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14529200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>14413900</v>
+      </c>
+      <c r="F47" s="3">
         <v>13725300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>13610000</v>
       </c>
-      <c r="F47" s="3">
-        <v>13717300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>13049100</v>
-      </c>
       <c r="H47" s="3">
+        <v>13721900</v>
+      </c>
+      <c r="I47" s="3">
+        <v>13053500</v>
+      </c>
+      <c r="J47" s="3">
         <v>14811600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>16594300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>12177700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>11902200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>16357200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>15484300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>15340400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>15455600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>13971300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>13243100</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>231800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>229900</v>
+      </c>
+      <c r="F48" s="3">
         <v>246800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>244700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>267500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>254500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>260500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>291900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>322900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>315600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>402200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>380700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>402000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>405000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>455400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>431600</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3386400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3359500</v>
+      </c>
+      <c r="F49" s="3">
         <v>3251100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3223800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3190200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3034800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3037300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3402900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3340000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3264400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3598500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3406500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3523500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3549900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4161600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3944700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,55 +2801,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>451100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>447500</v>
+      </c>
+      <c r="F52" s="3">
         <v>495600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>491400</v>
       </c>
-      <c r="F52" s="3">
-        <v>576900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>548800</v>
-      </c>
       <c r="H52" s="3">
+        <v>572300</v>
+      </c>
+      <c r="I52" s="3">
+        <v>544500</v>
+      </c>
+      <c r="J52" s="3">
         <v>349000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>391000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>294900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>288200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>590300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>558800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>593700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>598100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1061000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1005700</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2907,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20454500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>20292100</v>
+      </c>
+      <c r="F54" s="3">
         <v>19693800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>19528400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19775800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>18812500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>20548300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>23021600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>74533000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>72846400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>74170400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>70212300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>71904800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>72444800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>74888900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>70985700</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,35 +3006,37 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7647200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7586500</v>
+      </c>
+      <c r="F57" s="3">
         <v>7512000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7448900</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H57" s="3">
+        <v>6849100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>6515500</v>
+      </c>
+      <c r="J57" s="3">
         <v>5946500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6662300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2787,22 +3049,28 @@
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>7918800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>7506100</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>44600</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2811,10 +3079,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>39900</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2823,213 +3091,243 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>387200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>366500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>630900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>635700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>555300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>526300</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="D59" s="3">
+        <v>176400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>175000</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>264200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>251300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>455500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>510300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>53255900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>52050900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>25300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>25500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>28930200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>27422400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7873400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7810900</v>
+      </c>
+      <c r="F60" s="3">
         <v>7512000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7448900</v>
       </c>
-      <c r="F60" s="3">
-        <v>268100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>255100</v>
-      </c>
       <c r="H60" s="3">
+        <v>7159200</v>
+      </c>
+      <c r="I60" s="3">
+        <v>6810500</v>
+      </c>
+      <c r="J60" s="3">
         <v>6402000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7172600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>53261300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>52056100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>387200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>366500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>664200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>669200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>37404300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>35454800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1794500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1780300</v>
+      </c>
+      <c r="F61" s="3">
         <v>1521500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1508700</v>
       </c>
-      <c r="F61" s="3">
-        <v>1657400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1576600</v>
-      </c>
       <c r="H61" s="3">
+        <v>1887500</v>
+      </c>
+      <c r="I61" s="3">
+        <v>1795600</v>
+      </c>
+      <c r="J61" s="3">
         <v>1562600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1750700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1684700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1646600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>17833700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>16882000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>17672500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>17805300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>17103900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>16212500</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3569700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3541400</v>
+      </c>
+      <c r="F62" s="3">
         <v>3892100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3859400</v>
       </c>
-      <c r="F62" s="3">
-        <v>10809000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>10282500</v>
-      </c>
       <c r="H62" s="3">
+        <v>3687800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3508200</v>
+      </c>
+      <c r="J62" s="3">
         <v>3572000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4001900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>10290900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>10058000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>46492800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>44011700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>44659600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>44995000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>11326000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>10735700</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3479,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13253500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13148300</v>
+      </c>
+      <c r="F66" s="3">
         <v>12943600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12834800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12808600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12184700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11559500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12950800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>65269500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>63792600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>64794100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>61336400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>63030300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>63503700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>65933500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>62497100</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3712,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3765,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1549600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1537300</v>
+      </c>
+      <c r="F72" s="3">
         <v>1105300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1096000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1262000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1200600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1239600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1388800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>975400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>953400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>817300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>773700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>690800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>696000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>539000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>510900</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3977,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7168500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7111500</v>
+      </c>
+      <c r="F76" s="3">
         <v>6712900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6656500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6933700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6596000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8960300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10038800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9236700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9027700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9346300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8847500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8851900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>8918400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>8932900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>8467300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,60 +4083,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3804,8 +4194,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,55 +4219,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F83" s="3">
         <v>25400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>28400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>10700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>10400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>38500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>36500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>33000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>31200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>15500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>16900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>36000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4533,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>423400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>420000</v>
+      </c>
+      <c r="F89" s="3">
         <v>120400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>119400</v>
       </c>
-      <c r="F89" s="3">
-        <v>1087300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>1034400</v>
-      </c>
       <c r="H89" s="3">
+        <v>433000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>411900</v>
+      </c>
+      <c r="J89" s="3">
         <v>380300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>426100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>960800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>939000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-130500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-123600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>555600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>526700</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,8 +4611,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4218,8 +4660,14 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4766,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-184700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-183200</v>
+      </c>
+      <c r="F94" s="3">
         <v>100400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>99500</v>
       </c>
-      <c r="F94" s="3">
-        <v>400900</v>
-      </c>
-      <c r="G94" s="3">
-        <v>381400</v>
-      </c>
       <c r="H94" s="3">
+        <v>1029300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>979200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-467500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-523800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1227000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1199200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-331300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-313600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
         <v>176700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>167500</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,55 +4844,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>62800</v>
+      </c>
+      <c r="F96" s="3">
         <v>177100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>175600</v>
       </c>
-      <c r="F96" s="3">
-        <v>262900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>250100</v>
-      </c>
       <c r="H96" s="3">
+        <v>171100</v>
+      </c>
+      <c r="I96" s="3">
+        <v>162800</v>
+      </c>
+      <c r="J96" s="3">
         <v>173300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>194100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>145800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>142500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>86900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>82300</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
         <v>67600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>64100</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,145 +5052,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-238000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-236100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-346900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-343900</v>
       </c>
-      <c r="F100" s="3">
-        <v>-1385000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-1317500</v>
-      </c>
       <c r="H100" s="3">
+        <v>-1359100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-1292900</v>
+      </c>
+      <c r="J100" s="3">
         <v>-546400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-612200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>81700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>79900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-197000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-186500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>442100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>419100</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F101" s="3">
         <v>6200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>6900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-122700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-121700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>95700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>91100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-627500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-703000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-181500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-177400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-659200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-624000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>1174100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1112900</v>
       </c>
     </row>
